--- a/data/trans_orig/IP07A19-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP07A19-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de que le haya gustado ir al colegio en 2007 (tasa de respuesta: 99,2%)</t>
+          <t>Menores según la frecuencia de que le haya gustado ir al colegio, percibida por el adulto en 2007 (tasa de respuesta: 99,2%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10128</t>
+          <t>10292</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20554</t>
+          <t>20649</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3435</t>
+          <t>3329</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11465</t>
+          <t>11143</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15861</t>
+          <t>15452</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29228</t>
+          <t>28868</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>32,83%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19428</t>
+          <t>19280</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30732</t>
+          <t>30768</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18936</t>
+          <t>19155</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29167</t>
+          <t>28653</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>47,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>40903</t>
+          <t>42195</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>56191</t>
+          <t>57038</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>47,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>64,86%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2878</t>
+          <t>2745</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10647</t>
+          <t>10384</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3069</t>
+          <t>2935</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10341</t>
+          <t>10365</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7141</t>
+          <t>7169</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17041</t>
+          <t>17909</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>20,37%</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>703</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6504</t>
+          <t>5612</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>693</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5793</t>
+          <t>5944</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,76%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4999</t>
+          <t>4970</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4142</t>
+          <t>4480</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>720</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6329</t>
+          <t>6966</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,92%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7436</t>
+          <t>7333</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15517</t>
+          <t>15485</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6443</t>
+          <t>6340</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15081</t>
+          <t>14646</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15665</t>
+          <t>16009</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27350</t>
+          <t>28043</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>46,37%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9446</t>
+          <t>9414</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17537</t>
+          <t>18081</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>60,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7821</t>
+          <t>7748</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16661</t>
+          <t>16566</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>54,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>19798</t>
+          <t>19393</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>32186</t>
+          <t>31924</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>52,79%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1418</t>
+          <t>1460</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7379</t>
+          <t>7340</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2442</t>
+          <t>2619</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9276</t>
+          <t>9624</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5544</t>
+          <t>5563</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>14371</t>
+          <t>14876</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>24,6%</t>
         </is>
       </c>
     </row>
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>633</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5605</t>
+          <t>6375</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>624</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6347</t>
+          <t>6288</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,4%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4229</t>
+          <t>4284</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4768</t>
+          <t>4995</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5111</t>
+          <t>5589</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13774</t>
+          <t>13827</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4555</t>
+          <t>4661</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12953</t>
+          <t>12903</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11578</t>
+          <t>11771</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23748</t>
+          <t>23607</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>26,97%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13271</t>
+          <t>12666</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22994</t>
+          <t>22630</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>68,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21635</t>
+          <t>21670</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33324</t>
+          <t>33962</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>39,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>62,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>38608</t>
+          <t>37923</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>53532</t>
+          <t>53099</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>61,15%</t>
+          <t>60,66%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>787</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6493</t>
+          <t>6617</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10111</t>
+          <t>9909</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21064</t>
+          <t>20688</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>12232</t>
+          <t>11906</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>25196</t>
+          <t>24333</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>27,8%</t>
         </is>
       </c>
     </row>
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>690</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6756</t>
+          <t>6195</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>676</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6822</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,76%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>645</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6455</t>
+          <t>5636</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4595</t>
+          <t>4095</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7031</t>
+          <t>7165</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,19%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16975</t>
+          <t>17150</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30343</t>
+          <t>30618</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15871</t>
+          <t>15772</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>29509</t>
+          <t>28947</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>37098</t>
+          <t>36645</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>54854</t>
+          <t>55952</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,7%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>32752</t>
+          <t>32886</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>48117</t>
+          <t>47742</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>32822</t>
+          <t>32656</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>48002</t>
+          <t>48120</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>69576</t>
+          <t>69760</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>91140</t>
+          <t>92073</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>50,52%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11054</t>
+          <t>10668</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>22856</t>
+          <t>22082</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14117</t>
+          <t>14627</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>26946</t>
+          <t>27275</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>27737</t>
+          <t>28206</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>44515</t>
+          <t>44951</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,66%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2078</t>
+          <t>2537</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9426</t>
+          <t>10251</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2752</t>
+          <t>3321</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11027</t>
+          <t>11541</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6852</t>
+          <t>6639</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>17415</t>
+          <t>17582</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,65%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1231</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7631</t>
+          <t>8542</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2536</t>
+          <t>2604</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>10511</t>
+          <t>10019</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>5149</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>15104</t>
+          <t>15093</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,28%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>11911</t>
+          <t>12624</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>23225</t>
+          <t>23360</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>12428</t>
+          <t>12234</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>23532</t>
+          <t>24435</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>27471</t>
+          <t>27016</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>43713</t>
+          <t>43659</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,23%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>17067</t>
+          <t>16623</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>28820</t>
+          <t>28886</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>20536</t>
+          <t>19643</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>33344</t>
+          <t>32962</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>41030</t>
+          <t>40622</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>57451</t>
+          <t>58461</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>47,18%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>7442</t>
+          <t>7384</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>17437</t>
+          <t>17054</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>14299</t>
+          <t>14251</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>25335</t>
+          <t>26654</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>24807</t>
+          <t>24128</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>40116</t>
+          <t>39810</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,13%</t>
         </is>
       </c>
     </row>
@@ -3804,7 +3804,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3939</t>
+          <t>4033</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2685</t>
+          <t>2585</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>10279</t>
+          <t>9636</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2745</t>
+          <t>2701</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>11563</t>
+          <t>11526</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,3%</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4789</t>
+          <t>4780</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3439</t>
+          <t>3383</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>622</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5753</t>
+          <t>6246</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>7278</t>
+          <t>7190</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>16143</t>
+          <t>16790</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>3404</t>
+          <t>3342</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>10776</t>
+          <t>10790</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>12043</t>
+          <t>12781</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>24302</t>
+          <t>25537</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>32,89%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>15902</t>
+          <t>15384</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>26263</t>
+          <t>25995</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>62,22%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>10386</t>
+          <t>10190</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>19900</t>
+          <t>19525</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>28525</t>
+          <t>28639</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>42625</t>
+          <t>42387</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>54,59%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2998</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>11314</t>
+          <t>10659</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>6939</t>
+          <t>7281</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>15789</t>
+          <t>16181</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>11880</t>
+          <t>11766</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>23330</t>
+          <t>24343</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>31,35%</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>694</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>6048</t>
+          <t>6851</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>5186</t>
+          <t>4598</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>1498</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>8769</t>
+          <t>8549</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,01%</t>
         </is>
       </c>
     </row>
@@ -4599,7 +4599,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3363</t>
+          <t>3807</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>568</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>4954</t>
+          <t>4949</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>6402</t>
+          <t>5745</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>7,4%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>76189</t>
+          <t>76233</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>100778</t>
+          <t>99437</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>59749</t>
+          <t>59829</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>84014</t>
+          <t>83275</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>142327</t>
+          <t>143335</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>177563</t>
+          <t>178545</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,81%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>125975</t>
+          <t>126863</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>154285</t>
+          <t>153349</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>129645</t>
+          <t>130247</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>158524</t>
+          <t>158542</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>265427</t>
+          <t>266065</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>304991</t>
+          <t>305693</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>49,32%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>37187</t>
+          <t>37490</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>58355</t>
+          <t>57698</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>66300</t>
+          <t>65340</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>91004</t>
+          <t>90481</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>108856</t>
+          <t>107639</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>141131</t>
+          <t>139983</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,59%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>5112</t>
+          <t>4668</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>14649</t>
+          <t>14241</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>14494</t>
+          <t>14513</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>28354</t>
+          <t>28716</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>21090</t>
+          <t>21673</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>38407</t>
+          <t>39294</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,34%</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>6536</t>
+          <t>6511</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>16639</t>
+          <t>17355</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>6345</t>
+          <t>6439</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>16725</t>
+          <t>17049</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>14866</t>
+          <t>15674</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>30622</t>
+          <t>30241</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de que le haya gustado ir al colegio en 2012 (tasa de respuesta: 98,02%)</t>
+          <t>Menores según la frecuencia de que le haya gustado ir al colegio, percibida por el adulto en 2012 (tasa de respuesta: 98,02%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14062</t>
+          <t>13308</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24592</t>
+          <t>23971</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>60,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6468</t>
+          <t>6523</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15617</t>
+          <t>15173</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22319</t>
+          <t>22551</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36529</t>
+          <t>36119</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>48,55%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8899</t>
+          <t>9764</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19441</t>
+          <t>19715</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13388</t>
+          <t>13694</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22512</t>
+          <t>23140</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>66,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25558</t>
+          <t>24944</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39826</t>
+          <t>39381</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>52,94%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3033</t>
+          <t>3077</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10623</t>
+          <t>10805</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1540</t>
+          <t>1916</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8241</t>
+          <t>8321</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5938</t>
+          <t>6099</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16371</t>
+          <t>16109</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,65%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>641</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>5510</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>640</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5806</t>
+          <t>5465</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -6197,7 +6197,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3728</t>
+          <t>3691</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3625</t>
+          <t>3171</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9733</t>
+          <t>10146</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18993</t>
+          <t>19183</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,71%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11367</t>
+          <t>11530</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20974</t>
+          <t>20567</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23844</t>
+          <t>24149</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37513</t>
+          <t>37933</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,73%</t>
+          <t>54,33%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10748</t>
+          <t>10745</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20410</t>
+          <t>19917</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8565</t>
+          <t>8353</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17992</t>
+          <t>17494</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>20810</t>
+          <t>21122</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>34434</t>
+          <t>34658</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>49,64%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2046</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9009</t>
+          <t>9143</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1341</t>
+          <t>1330</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7514</t>
+          <t>7638</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4472</t>
+          <t>4463</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>13692</t>
+          <t>13310</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,06%</t>
         </is>
       </c>
     </row>
@@ -6766,7 +6766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2717</t>
+          <t>3630</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>650</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>6272</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1230</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7133</t>
+          <t>6847</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>9,81%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11593</t>
+          <t>11245</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22212</t>
+          <t>22087</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5107</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13228</t>
+          <t>13016</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19272</t>
+          <t>18439</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32041</t>
+          <t>31883</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>41,77%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16905</t>
+          <t>16576</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27573</t>
+          <t>27982</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>63,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8636</t>
+          <t>9149</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18005</t>
+          <t>17640</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>55,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>27826</t>
+          <t>28230</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>41941</t>
+          <t>42136</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>55,2%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>756</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6567</t>
+          <t>6246</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3845</t>
+          <t>4156</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11243</t>
+          <t>11424</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6034</t>
+          <t>5800</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>16153</t>
+          <t>15024</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>19,68%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>666</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>5916</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>627</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5874</t>
+          <t>5692</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2174</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9861</t>
+          <t>9073</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>11,89%</t>
         </is>
       </c>
     </row>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2578</t>
+          <t>2284</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7596,7 +7596,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3130</t>
+          <t>2836</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7611,7 +7611,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3546</t>
+          <t>3823</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7646,7 +7646,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30863</t>
+          <t>30910</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45863</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,82 +7801,82 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
+          <t>35,59%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>52,69%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>38245</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>30909</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>46174</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>38,2%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>30,87%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>46,11%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>76999</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>66431</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>88455</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>41,18%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>35,53%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>52,8%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>38245</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>30333</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>46336</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>38,2%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>30,29%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>46,28%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>76999</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>66007</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>89989</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>41,18%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>35,3%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>47,31%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>25623</t>
+          <t>25896</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>40973</t>
+          <t>40720</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>46,88%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>29855</t>
+          <t>29910</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>46886</t>
+          <t>45837</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>59235</t>
+          <t>60101</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>82303</t>
+          <t>81419</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>43,54%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5767</t>
+          <t>5872</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15808</t>
+          <t>16317</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7266</t>
+          <t>7045</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17567</t>
+          <t>17556</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>15436</t>
+          <t>14792</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>29973</t>
+          <t>29551</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,8%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>756</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6630</t>
+          <t>6691</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5303</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15158</t>
+          <t>16137</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7309</t>
+          <t>6952</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>19883</t>
+          <t>18252</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>595</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5852</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1211</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6904</t>
+          <t>7147</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2585</t>
+          <t>2181</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>10749</t>
+          <t>10276</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>22227</t>
+          <t>23318</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>37161</t>
+          <t>37420</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>18724</t>
+          <t>17592</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>31231</t>
+          <t>30956</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>44889</t>
+          <t>45400</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>64552</t>
+          <t>64204</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>43,73%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>22204</t>
+          <t>22276</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>36413</t>
+          <t>35922</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>19721</t>
+          <t>20395</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>32852</t>
+          <t>33994</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>46189</t>
+          <t>45329</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>64951</t>
+          <t>64827</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>44,16%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5026</t>
+          <t>5175</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>14939</t>
+          <t>14846</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>8731</t>
+          <t>8438</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>19967</t>
+          <t>19022</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>16390</t>
+          <t>16028</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>31005</t>
+          <t>30431</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>20,73%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>7421</t>
+          <t>7019</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1373</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>7765</t>
+          <t>7531</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3798</t>
+          <t>3461</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>11776</t>
+          <t>11559</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>1323</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>7117</t>
+          <t>7362</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1502</t>
+          <t>1820</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>8152</t>
+          <t>8541</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3931</t>
+          <t>3754</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>12438</t>
+          <t>12670</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,63%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>4896</t>
+          <t>4858</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>12698</t>
+          <t>12536</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>7133</t>
+          <t>7321</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>16523</t>
+          <t>16086</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>14468</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>26194</t>
+          <t>26252</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>42,14%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>4443</t>
+          <t>4902</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>12529</t>
+          <t>12689</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>11469</t>
+          <t>11530</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>21094</t>
+          <t>21621</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>17737</t>
+          <t>18822</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>30192</t>
+          <t>30088</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>48,3%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3200</t>
+          <t>3374</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>9887</t>
+          <t>10207</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2844</t>
+          <t>2826</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>10817</t>
+          <t>10524</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>7348</t>
+          <t>7517</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>17692</t>
+          <t>17998</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,89%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>653</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>5600</t>
+          <t>5659</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>620</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5531</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1440</t>
+          <t>1412</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>8106</t>
+          <t>8371</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,44%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>575</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>5019</t>
+          <t>5072</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>580</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>112155</t>
+          <t>113829</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>140922</t>
+          <t>140521</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>95762</t>
+          <t>96038</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>123385</t>
+          <t>122876</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>214579</t>
+          <t>216402</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>255626</t>
+          <t>253354</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>41,09%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>108605</t>
+          <t>107506</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>135879</t>
+          <t>135860</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,7 +9960,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>110972</t>
+          <t>111421</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>138864</t>
+          <t>138751</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>226374</t>
+          <t>227169</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>265904</t>
+          <t>266283</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>43,18%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>30144</t>
+          <t>30087</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>49655</t>
+          <t>50056</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>36439</t>
+          <t>37260</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>56922</t>
+          <t>57908</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>71843</t>
+          <t>72291</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>99569</t>
+          <t>99398</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,12%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>6729</t>
+          <t>6240</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>17933</t>
+          <t>17926</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>16166</t>
+          <t>15975</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>30511</t>
+          <t>30480</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>25036</t>
+          <t>24717</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>42614</t>
+          <t>43150</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,0%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>3503</t>
+          <t>3352</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>12295</t>
+          <t>12231</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>5561</t>
+          <t>5832</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>15321</t>
+          <t>15284</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10334,47 +10334,47 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
+          <t>1,87%</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>4,91%</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>16263</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>10961</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>23973</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>2,64%</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
           <t>1,78%</t>
         </is>
       </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>4,92%</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>16263</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t>10967</t>
-        </is>
-      </c>
-      <c r="T44" s="2" t="inlineStr">
-        <is>
-          <t>23493</t>
-        </is>
-      </c>
-      <c r="U44" s="2" t="inlineStr">
-        <is>
-          <t>2,64%</t>
-        </is>
-      </c>
-      <c r="V44" s="2" t="inlineStr">
-        <is>
-          <t>1,78%</t>
-        </is>
-      </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de que le haya gustado ir al colegio en 2016 (tasa de respuesta: 98,62%)</t>
+          <t>Menores según la frecuencia de que le haya gustado ir al colegio, percibida por el adulto en 2016 (tasa de respuesta: 98,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12099</t>
+          <t>11422</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21192</t>
+          <t>20891</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61,22%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>10300</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21071</t>
+          <t>20595</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>53,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24812</t>
+          <t>24906</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39293</t>
+          <t>38900</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>53,35%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9664</t>
+          <t>9585</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19287</t>
+          <t>18994</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>54,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11867</t>
+          <t>12328</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22259</t>
+          <t>22968</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>59,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24210</t>
+          <t>25389</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38796</t>
+          <t>39101</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>53,63%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4822</t>
+          <t>5535</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2053</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8721</t>
+          <t>8769</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3389</t>
+          <t>3568</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11247</t>
+          <t>11548</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,84%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>578</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5025</t>
+          <t>5447</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11127,7 +11127,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3390</t>
+          <t>3678</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11142,7 +11142,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>739</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6242</t>
+          <t>6360</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,72%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14614</t>
+          <t>14475</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26496</t>
+          <t>25777</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11445,12 +11445,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12705</t>
+          <t>12951</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23618</t>
+          <t>23942</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>50,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30364</t>
+          <t>30804</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46560</t>
+          <t>47431</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>47,33%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14187</t>
+          <t>14366</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25889</t>
+          <t>25711</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11899</t>
+          <t>12013</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22857</t>
+          <t>23076</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>48,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>28130</t>
+          <t>28511</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>45014</t>
+          <t>44893</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>44,8%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5533</t>
+          <t>5676</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15068</t>
+          <t>15237</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6990</t>
+          <t>7076</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17162</t>
+          <t>16785</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>14609</t>
+          <t>14878</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>28719</t>
+          <t>29791</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>29,73%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>784</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6727</t>
+          <t>7309</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3788</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1424</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8421</t>
+          <t>8204</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,19%</t>
         </is>
       </c>
     </row>
@@ -11922,7 +11922,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3607</t>
+          <t>3566</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11937,7 +11937,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11957,7 +11957,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3593</t>
+          <t>3600</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8799</t>
+          <t>8525</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17487</t>
+          <t>17475</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12127,12 +12127,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>62,23%</t>
+          <t>62,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>6679</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15394</t>
+          <t>15950</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17401</t>
+          <t>17116</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30793</t>
+          <t>30741</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>44,48%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4488</t>
+          <t>4585</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12505</t>
+          <t>12952</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15017</t>
+          <t>15336</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26028</t>
+          <t>25459</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>62,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>22688</t>
+          <t>23035</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>35725</t>
+          <t>37403</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>54,12%</t>
         </is>
       </c>
     </row>
@@ -12338,12 +12338,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>724</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6355</t>
+          <t>6539</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12353,12 +12353,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4043</t>
+          <t>3503</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12113</t>
+          <t>11534</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5579</t>
+          <t>5566</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>14966</t>
+          <t>15187</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,98%</t>
         </is>
       </c>
     </row>
@@ -12451,12 +12451,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>628</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6309</t>
+          <t>6513</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12466,12 +12466,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12486,12 +12486,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>707</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5569</t>
+          <t>5533</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12521,12 +12521,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1711</t>
+          <t>1714</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9384</t>
+          <t>8877</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12541,7 +12541,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -12569,7 +12569,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5192</t>
+          <t>5701</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12584,7 +12584,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12604,7 +12604,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3340</t>
+          <t>3460</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12619,7 +12619,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>638</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6368</t>
+          <t>6279</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12654,7 +12654,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,09%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>37534</t>
+          <t>37778</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>54786</t>
+          <t>56224</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>33072</t>
+          <t>33101</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>50015</t>
+          <t>49545</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>48,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>74839</t>
+          <t>76201</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>99123</t>
+          <t>98327</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>45,09%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>31967</t>
+          <t>31923</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>49130</t>
+          <t>49168</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>27293</t>
+          <t>27683</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>43598</t>
+          <t>43635</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>63764</t>
+          <t>64230</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>87336</t>
+          <t>87228</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>40,0%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16458</t>
+          <t>16202</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>31268</t>
+          <t>30729</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>13425</t>
+          <t>13007</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>26226</t>
+          <t>26265</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>32129</t>
+          <t>32147</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>51567</t>
+          <t>52099</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,89%</t>
         </is>
       </c>
     </row>
@@ -13133,12 +13133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>728</t>
+          <t>622</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6774</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2208</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10918</t>
+          <t>10197</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13183,12 +13183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4320</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14314</t>
+          <t>13755</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13218,12 +13218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,31%</t>
         </is>
       </c>
     </row>
@@ -13246,12 +13246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>757</t>
+          <t>659</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6915</t>
+          <t>6671</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13261,12 +13261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>692</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6353</t>
+          <t>6818</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13296,12 +13296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2719</t>
+          <t>2627</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>10375</t>
+          <t>10258</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13331,12 +13331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>26412</t>
+          <t>26590</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>40643</t>
+          <t>40543</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>19077</t>
+          <t>19519</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>33776</t>
+          <t>33549</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>50527</t>
+          <t>49608</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>70335</t>
+          <t>69773</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>47,11%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>20647</t>
+          <t>20762</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>33823</t>
+          <t>33737</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>19271</t>
+          <t>20270</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>33509</t>
+          <t>33933</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>44320</t>
+          <t>44309</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>63985</t>
+          <t>63269</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13679,7 +13679,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>42,72%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6513</t>
+          <t>6411</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>16461</t>
+          <t>16410</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5813</t>
+          <t>5801</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>16194</t>
+          <t>15462</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>14998</t>
+          <t>14455</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>28868</t>
+          <t>28612</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,32%</t>
         </is>
       </c>
     </row>
@@ -13815,12 +13815,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>517</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4806</t>
+          <t>4851</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13830,12 +13830,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13850,12 +13850,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3568</t>
+          <t>3805</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>13107</t>
+          <t>12748</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13865,12 +13865,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>5042</t>
+          <t>5582</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>15287</t>
+          <t>15313</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13900,12 +13900,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,34%</t>
         </is>
       </c>
     </row>
@@ -13928,12 +13928,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>633</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5420</t>
+          <t>5992</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13943,12 +13943,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13963,12 +13963,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>694</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>6588</t>
+          <t>7014</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13983,7 +13983,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1474</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>9014</t>
+          <t>9181</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14013,12 +14013,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -14158,12 +14158,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>7183</t>
+          <t>7230</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>15778</t>
+          <t>16500</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>7650</t>
+          <t>8285</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>17800</t>
+          <t>17639</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>17190</t>
+          <t>17685</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>30208</t>
+          <t>31102</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>43,9%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>8993</t>
+          <t>8452</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>18473</t>
+          <t>18150</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>57,38%</t>
+          <t>56,38%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>9647</t>
+          <t>9177</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>19925</t>
+          <t>18990</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>21368</t>
+          <t>21239</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>34559</t>
+          <t>34470</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>48,65%</t>
         </is>
       </c>
     </row>
@@ -14384,12 +14384,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2666</t>
+          <t>3109</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>9825</t>
+          <t>10182</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>7138</t>
+          <t>7056</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>16212</t>
+          <t>16487</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14434,12 +14434,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>11990</t>
+          <t>11334</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>24232</t>
+          <t>23428</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>33,07%</t>
         </is>
       </c>
     </row>
@@ -14502,7 +14502,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4504</t>
+          <t>4240</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14517,7 +14517,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14537,7 +14537,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3927</t>
+          <t>4014</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14552,7 +14552,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>674</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>5910</t>
+          <t>5796</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14587,7 +14587,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,18%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>125241</t>
+          <t>125680</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>156634</t>
+          <t>155778</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>107752</t>
+          <t>109517</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>138526</t>
+          <t>139056</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>243303</t>
+          <t>243054</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>287992</t>
+          <t>287130</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,27%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>107826</t>
+          <t>109620</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>137458</t>
+          <t>138633</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>116339</t>
+          <t>116551</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>145903</t>
+          <t>145574</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>233436</t>
+          <t>232540</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>274375</t>
+          <t>275316</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>40,53%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>42844</t>
+          <t>42297</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>65248</t>
+          <t>66021</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>51281</t>
+          <t>52633</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>75947</t>
+          <t>76332</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>101038</t>
+          <t>101608</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>133491</t>
+          <t>135649</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,97%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>8450</t>
+          <t>7886</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>20318</t>
+          <t>19895</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>11009</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>24578</t>
+          <t>24949</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>22570</t>
+          <t>22436</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>40981</t>
+          <t>40807</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -15292,12 +15292,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>3284</t>
+          <t>3250</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>11794</t>
+          <t>11762</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15307,12 +15307,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>2768</t>
+          <t>3426</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>11884</t>
+          <t>12371</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15342,12 +15342,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>7520</t>
+          <t>8152</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>19464</t>
+          <t>20574</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
